--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.79893736725859</v>
+        <v>11.01732732217952</v>
       </c>
       <c r="D2" t="n">
-        <v>67.16657735386225</v>
+        <v>10.91456882000262</v>
       </c>
       <c r="E2" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F2" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.5203028971122</v>
+        <v>7.234549220780732</v>
       </c>
       <c r="D3" t="n">
-        <v>44.03420386318628</v>
+        <v>7.155558127767771</v>
       </c>
       <c r="E3" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F3" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.86326680853125</v>
+        <v>10.54028085638633</v>
       </c>
       <c r="D4" t="n">
-        <v>64.06868035581428</v>
+        <v>10.41116055781982</v>
       </c>
       <c r="E4" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F4" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.76166544173525</v>
+        <v>4.511270634281978</v>
       </c>
       <c r="D5" t="n">
-        <v>27.57755770771529</v>
+        <v>4.481353127503734</v>
       </c>
       <c r="E5" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F5" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.47420009666833</v>
+        <v>9.014557515708605</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66844737783996</v>
+        <v>8.883622698898995</v>
       </c>
       <c r="E6" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F6" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.82453858498697</v>
+        <v>5.658987520060382</v>
       </c>
       <c r="D7" t="n">
-        <v>35.14463196945593</v>
+        <v>5.711002695036589</v>
       </c>
       <c r="E7" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F7" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.17769097361405</v>
+        <v>7.178874783212283</v>
       </c>
       <c r="D8" t="n">
-        <v>43.38551767743888</v>
+        <v>7.050146622583819</v>
       </c>
       <c r="E8" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F8" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.61977487189392</v>
+        <v>3.838213416682762</v>
       </c>
       <c r="D9" t="n">
-        <v>22.84066709718116</v>
+        <v>3.711608403291938</v>
       </c>
       <c r="E9" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F9" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.90692126784687</v>
+        <v>2.909874706025117</v>
       </c>
       <c r="D10" t="n">
-        <v>18.17330428299802</v>
+        <v>2.953161945987179</v>
       </c>
       <c r="E10" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F10" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.04475148201161</v>
+        <v>3.257272115826886</v>
       </c>
       <c r="D11" t="n">
-        <v>19.31464908051755</v>
+        <v>3.138630475584101</v>
       </c>
       <c r="E11" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F11" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.80897193686042</v>
+        <v>7.606457939739818</v>
       </c>
       <c r="D12" t="n">
-        <v>46.1148004525755</v>
+        <v>7.493655073543519</v>
       </c>
       <c r="E12" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F12" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.05596509032343</v>
+        <v>8.621594327177556</v>
       </c>
       <c r="D13" t="n">
-        <v>53.86789727821643</v>
+        <v>8.753533307710169</v>
       </c>
       <c r="E13" t="n">
-        <v>16.27897240072847</v>
+        <v>2.645333015118377</v>
       </c>
       <c r="F13" t="n">
-        <v>16.18708468676696</v>
+        <v>2.630401261599631</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
